--- a/ΕΝΗΜΕΡΩΤΙΚΑ_ΣΗΜΕΙΩΜΑΤΑ/2026-02/XLSX/ΕΝΗΜΕΡΩΤΙΚΟ_ΣΗΜΕΙΩΜΑ_LIVERSOL_ΜΟΝΟΠΡΟΣΩΠΗ_Ι.Κ.Ε._(164)_2026-02.xlsx
+++ b/ΕΝΗΜΕΡΩΤΙΚΑ_ΣΗΜΕΙΩΜΑΤΑ/2026-02/XLSX/ΕΝΗΜΕΡΩΤΙΚΟ_ΣΗΜΕΙΩΜΑ_LIVERSOL_ΜΟΝΟΠΡΟΣΩΠΗ_Ι.Κ.Ε._(164)_2026-02.xlsx
@@ -2845,7 +2845,7 @@
     <row r="6" ht="60.75" customFormat="1" customHeight="1" s="10">
       <c r="B6" s="80" t="inlineStr">
         <is>
-          <t>06/03/26</t>
+          <t>09/03/26</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
@@ -3197,13 +3197,13 @@
         <v>1340.4</v>
       </c>
       <c r="E23" s="25" t="n">
-        <v>0</v>
+        <v>33.814131</v>
       </c>
       <c r="F23" s="25" t="n">
         <v>1.34</v>
       </c>
       <c r="G23" s="92" t="n">
-        <v>0</v>
+        <v>25.23</v>
       </c>
       <c r="H23" s="93" t="n"/>
     </row>
@@ -3237,13 +3237,13 @@
         <v>2369.06</v>
       </c>
       <c r="E25" s="25" t="n">
-        <v>0</v>
+        <v>23.4645906</v>
       </c>
       <c r="F25" s="25" t="n">
         <v>2.37</v>
       </c>
       <c r="G25" s="92" t="n">
-        <v>0</v>
+        <v>9.9</v>
       </c>
       <c r="H25" s="93" t="n"/>
     </row>
@@ -3417,13 +3417,13 @@
         <v>3256.6</v>
       </c>
       <c r="E34" s="25" t="n">
-        <v>0</v>
+        <v>12.8720652</v>
       </c>
       <c r="F34" s="25" t="n">
         <v>3.26</v>
       </c>
       <c r="G34" s="92" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="H34" s="93" t="n"/>
     </row>
@@ -3437,13 +3437,13 @@
         <v>3220.2</v>
       </c>
       <c r="E35" s="25" t="n">
-        <v>17.309193</v>
+        <v>13.5385114</v>
       </c>
       <c r="F35" s="25" t="n">
         <v>3.22</v>
       </c>
       <c r="G35" s="92" t="n">
-        <v>5.38</v>
+        <v>4.2</v>
       </c>
       <c r="H35" s="93" t="n"/>
     </row>
@@ -3457,13 +3457,13 @@
         <v>3180.02</v>
       </c>
       <c r="E36" s="25" t="n">
-        <v>0</v>
+        <v>49.3762744</v>
       </c>
       <c r="F36" s="25" t="n">
         <v>3.18</v>
       </c>
       <c r="G36" s="92" t="n">
-        <v>0</v>
+        <v>15.53</v>
       </c>
       <c r="H36" s="93" t="n"/>
     </row>
@@ -3477,13 +3477,13 @@
         <v>2225.96</v>
       </c>
       <c r="E37" s="25" t="n">
-        <v>0</v>
+        <v>7.011383599999999</v>
       </c>
       <c r="F37" s="25" t="n">
         <v>2.23</v>
       </c>
       <c r="G37" s="92" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="H37" s="93" t="n"/>
     </row>
@@ -3497,13 +3497,13 @@
         <v>48729.26</v>
       </c>
       <c r="E38" s="95" t="n">
-        <v>1244.42</v>
+        <v>1367.18</v>
       </c>
       <c r="F38" s="95" t="n">
         <v>48.73</v>
       </c>
       <c r="G38" s="96" t="n">
-        <v>25.54</v>
+        <v>28.06</v>
       </c>
       <c r="H38" s="93" t="n"/>
     </row>
@@ -3602,7 +3602,7 @@
       </c>
       <c r="G46" s="83" t="n"/>
       <c r="H46" s="105" t="n">
-        <v>1244.42</v>
+        <v>1367.18</v>
       </c>
       <c r="I46" s="45" t="n"/>
     </row>
@@ -3707,7 +3707,7 @@
       </c>
       <c r="C53" s="110" t="inlineStr">
         <is>
-          <t>08/03/26</t>
+          <t>11/03/26</t>
         </is>
       </c>
       <c r="D53" s="111" t="n"/>
